--- a/카드_아키타입/06_크림.xlsx
+++ b/카드_아키타입/06_크림.xlsx
@@ -6206,7 +6206,7 @@
       <row>389</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="241" name="Image 241" descr="Picture"/>
@@ -6481,7 +6481,7 @@
       <row>408</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="771525" cy="1047750"/>
+    <ext cx="781050" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="252" name="Image 252" descr="Picture"/>
@@ -9506,7 +9506,7 @@
       <row>722</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="373" name="Image 373" descr="Picture"/>
@@ -9581,7 +9581,7 @@
       <row>741</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="904875"/>
+    <ext cx="1047750" cy="895350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="376" name="Image 376" descr="Picture"/>
@@ -11206,7 +11206,7 @@
       <row>868</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="933450"/>
+    <ext cx="1047750" cy="923925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="441" name="Image 441" descr="Picture"/>
@@ -11381,7 +11381,7 @@
       <row>883</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="448" name="Image 448" descr="Picture"/>
@@ -15506,7 +15506,7 @@
       <row>1228</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="613" name="Image 613" descr="Picture"/>
